--- a/branches/readme-rc4/StructureDefinition-mii-ex-labor-interpretationsbeeinflussende-eigenschaft.xlsx
+++ b/branches/readme-rc4/StructureDefinition-mii-ex-labor-interpretationsbeeinflussende-eigenschaft.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T12:19:33+00:00</t>
+    <t>2026-09-08T12:37:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
